--- a/projetos/OBRA_TMULT/05_SUPRIMENTOS_E_FINANCEIRO/FLUXO_DE_CAIXA_TMULT.xlsx
+++ b/projetos/OBRA_TMULT/05_SUPRIMENTOS_E_FINANCEIRO/FLUXO_DE_CAIXA_TMULT.xlsx
@@ -155,85 +155,125 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -944,6 +984,8 @@
           <t>Preço Global Turnkey da Obra</t>
         </is>
       </c>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
       <c r="E6" s="5" t="n">
         <v>1660762.28</v>
       </c>
@@ -954,6 +996,8 @@
           <t>Custo Direto Total da Obra</t>
         </is>
       </c>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
       <c r="E7" s="7" t="n">
         <v>1314562.67</v>
       </c>
@@ -964,8 +1008,10 @@
           <t>Total de Impostos s/ Faturamento (8,65%)</t>
         </is>
       </c>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
       <c r="E8" s="5" t="n">
-        <v>143655.92</v>
+        <v>143655.93</v>
       </c>
     </row>
     <row r="9">
@@ -974,6 +1020,8 @@
           <t>Despesas Administrativas Centrais BDI</t>
         </is>
       </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
       <c r="E9" s="7" t="n">
         <v>98649.3</v>
       </c>
@@ -984,7 +1032,9 @@
           <t>Lucro Líquido Operacional Realizado</t>
         </is>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="10" t="n">
         <v>103894.45</v>
       </c>
     </row>
@@ -994,8 +1044,10 @@
           <t>Margem Líquida Realizada sobre Venda</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>0.06255829100357459</v>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="11" t="n">
+        <v>0.06255829100357457</v>
       </c>
     </row>
     <row r="12">
@@ -1004,18 +1056,22 @@
           <t>Retenção Contratual Técnica (5,0%)</t>
         </is>
       </c>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
       <c r="E12" s="5" t="n">
         <v>83038.11</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>NECESSIDADE MÍNIMA DE CAPITAL DE GIRO</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
-        <v>180621.7</v>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="14" t="n">
+        <v>173437.91</v>
       </c>
     </row>
     <row r="14">
@@ -1024,7 +1080,9 @@
           <t>Mês de Máxima Exposição de Caixa</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>Mês 3 (Pico da Envoltória)</t>
         </is>
@@ -1036,52 +1094,54 @@
           <t>Ponto de Equilíbrio do Caixa (Break-even)</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>Mês 7 (Liquidação do TRD)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Período</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Entradas (R$)</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Saídas (R$)</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Saldo Mês (R$)</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Saldo Acumulado (R$)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Mês 1</t>
         </is>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="5" t="n">
         <v>105467.76</v>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="E18" s="5" t="n">
         <v>-105467.76</v>
       </c>
       <c r="F18" s="18" t="n">
@@ -1094,36 +1154,36 @@
           <t>Mês 2</t>
         </is>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="7" t="n">
         <v>155269.92</v>
       </c>
-      <c r="D19" s="20" t="n">
+      <c r="D19" s="7" t="n">
         <v>202190.46</v>
       </c>
-      <c r="E19" s="20" t="n">
+      <c r="E19" s="7" t="n">
         <v>-46920.54</v>
       </c>
-      <c r="F19" s="21" t="n">
+      <c r="F19" s="20" t="n">
         <v>-152388.3</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Mês 3</t>
         </is>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C20" s="5" t="n">
         <v>264001.06</v>
       </c>
-      <c r="D20" s="17" t="n">
-        <v>292234.46</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>-28233.4</v>
+      <c r="D20" s="5" t="n">
+        <v>285050.67</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-21049.61</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>-180621.7</v>
+        <v>-173437.91</v>
       </c>
     </row>
     <row r="21">
@@ -1132,36 +1192,36 @@
           <t>Mês 4</t>
         </is>
       </c>
-      <c r="C21" s="20" t="n">
-        <v>348054.46</v>
-      </c>
-      <c r="D21" s="20" t="n">
-        <v>290517.52</v>
-      </c>
-      <c r="E21" s="20" t="n">
-        <v>57536.94</v>
-      </c>
-      <c r="F21" s="21" t="n">
-        <v>-123084.76</v>
+      <c r="C21" s="7" t="n">
+        <v>329961.79</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>283390.75</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>46571.04</v>
+      </c>
+      <c r="F21" s="20" t="n">
+        <v>-126866.87</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>Mês 5</t>
         </is>
       </c>
-      <c r="C22" s="17" t="n">
-        <v>233397.32</v>
-      </c>
-      <c r="D22" s="17" t="n">
-        <v>259914.12</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>-26516.8</v>
+      <c r="C22" s="5" t="n">
+        <v>239197.61</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>267817.95</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-28620.34</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>-149601.56</v>
+        <v>-155487.21</v>
       </c>
     </row>
     <row r="23">
@@ -1170,54 +1230,54 @@
           <t>Mês 6</t>
         </is>
       </c>
-      <c r="C23" s="20" t="n">
-        <v>304396.06</v>
-      </c>
-      <c r="D23" s="20" t="n">
-        <v>287957.98</v>
-      </c>
-      <c r="E23" s="20" t="n">
-        <v>16438.08</v>
-      </c>
-      <c r="F23" s="21" t="n">
+      <c r="C23" s="7" t="n">
+        <v>316688.44</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>294364.71</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>22323.73</v>
+      </c>
+      <c r="F23" s="20" t="n">
         <v>-133163.48</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>Mês 7</t>
         </is>
       </c>
-      <c r="C24" s="17" t="n">
+      <c r="C24" s="5" t="n">
         <v>355643.46</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="5" t="n">
         <v>118585.53</v>
       </c>
-      <c r="E24" s="17" t="n">
+      <c r="E24" s="5" t="n">
         <v>237057.93</v>
       </c>
-      <c r="F24" s="22" t="n">
+      <c r="F24" s="21" t="n">
         <v>103894.45</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="C25" s="24" t="n">
+      <c r="C25" s="23" t="n">
         <v>1660762.28</v>
       </c>
-      <c r="D25" s="24" t="n">
+      <c r="D25" s="23" t="n">
         <v>1556867.83</v>
       </c>
-      <c r="E25" s="24" t="n">
+      <c r="E25" s="23" t="n">
         <v>103894.45</v>
       </c>
-      <c r="F25" s="24" t="n">
+      <c r="F25" s="23" t="n">
         <v>103894.45</v>
       </c>
     </row>
@@ -1271,63 +1331,72 @@
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Conta / Rubrica Operacional</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Natureza Contábil</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Mês 1</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Mês 2</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Mês 3</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Mês 4</t>
         </is>
       </c>
-      <c r="G2" s="15" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Mês 5</t>
         </is>
       </c>
-      <c r="H2" s="15" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Mês 6</t>
         </is>
       </c>
-      <c r="I2" s="15" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Mês 7</t>
         </is>
       </c>
-      <c r="J2" s="15" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Total Global (R$)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>1. ENTRADAS DE CAIXA (RECEBIMENTOS DE MEDIÇÕES)</t>
         </is>
       </c>
+      <c r="B3" s="24" t="n"/>
+      <c r="C3" s="24" t="n"/>
+      <c r="D3" s="24" t="n"/>
+      <c r="E3" s="24" t="n"/>
+      <c r="F3" s="24" t="n"/>
+      <c r="G3" s="24" t="n"/>
+      <c r="H3" s="24" t="n"/>
+      <c r="I3" s="24" t="n"/>
+      <c r="J3" s="24" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1335,105 +1404,105 @@
           <t>1.1 Faturamento Bruto de Medições</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
-        <is>
-          <t>Medição EAP</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="n">
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>Receita Bruta</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
         <v>163442.02</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="7" t="n">
         <v>277895.85</v>
       </c>
-      <c r="E4" s="20" t="n">
-        <v>366373.12</v>
-      </c>
-      <c r="F4" s="20" t="n">
-        <v>245681.39</v>
-      </c>
-      <c r="G4" s="20" t="n">
-        <v>320416.9</v>
-      </c>
-      <c r="H4" s="20" t="n">
+      <c r="E4" s="7" t="n">
+        <v>347328.2</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>251786.96</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>333356.25</v>
+      </c>
+      <c r="H4" s="7" t="n">
         <v>286953</v>
       </c>
-      <c r="I4" s="20" t="n">
+      <c r="I4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="27" t="n">
+      <c r="J4" s="25" t="n">
         <v>1660762.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1.2 Retenção Técnica Contratual (5,0%)</t>
-        </is>
-      </c>
-      <c r="B5" s="28" t="inlineStr">
-        <is>
-          <t>Dedução Contratual</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="n">
+          <t>1.2 Retenção Técnica Contratual (5%)</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Dedução</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>8172.1</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="5" t="n">
         <v>13894.79</v>
       </c>
-      <c r="E5" s="17" t="n">
-        <v>18318.66</v>
-      </c>
-      <c r="F5" s="17" t="n">
-        <v>12284.07</v>
-      </c>
-      <c r="G5" s="17" t="n">
-        <v>16020.84</v>
-      </c>
-      <c r="H5" s="17" t="n">
+      <c r="E5" s="5" t="n">
+        <v>17366.41</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>12589.35</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>16667.81</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>14347.65</v>
       </c>
-      <c r="I5" s="17" t="n">
+      <c r="I5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="29" t="n">
+      <c r="J5" s="26" t="n">
         <v>83038.11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1.3 Faturamento Líquido de Medições (95%)</t>
-        </is>
-      </c>
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t>Receita Faturada</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="n">
+          <t>1.3 Faturamento Líquido de Medições</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Receita Líquida</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
         <v>155269.92</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="7" t="n">
         <v>264001.06</v>
       </c>
-      <c r="E6" s="20" t="n">
-        <v>348054.46</v>
-      </c>
-      <c r="F6" s="20" t="n">
-        <v>233397.32</v>
-      </c>
-      <c r="G6" s="20" t="n">
-        <v>304396.06</v>
-      </c>
-      <c r="H6" s="20" t="n">
+      <c r="E6" s="7" t="n">
+        <v>329961.79</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>239197.61</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>316688.44</v>
+      </c>
+      <c r="H6" s="7" t="n">
         <v>272605.35</v>
       </c>
-      <c r="I6" s="20" t="n">
+      <c r="I6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="27" t="n">
+      <c r="J6" s="25" t="n">
         <v>1577724.17</v>
       </c>
     </row>
@@ -1443,69 +1512,69 @@
           <t>1.4 Recebimento Efetivo de Medições (D+15)</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Inflow</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="5" t="n">
         <v>155269.92</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="5" t="n">
         <v>264001.06</v>
       </c>
-      <c r="F7" s="17" t="n">
-        <v>348054.46</v>
-      </c>
-      <c r="G7" s="17" t="n">
-        <v>233397.32</v>
-      </c>
-      <c r="H7" s="17" t="n">
-        <v>304396.06</v>
-      </c>
-      <c r="I7" s="17" t="n">
+      <c r="F7" s="5" t="n">
+        <v>329961.79</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>239197.61</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>316688.44</v>
+      </c>
+      <c r="I7" s="5" t="n">
         <v>272605.35</v>
       </c>
-      <c r="J7" s="29" t="n">
+      <c r="J7" s="26" t="n">
         <v>1577724.17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1.5 Devolução da Retenção Técnica (TRD / Mês 7)</t>
-        </is>
-      </c>
-      <c r="B8" s="26" t="inlineStr">
+          <t>1.5 Devolução da Retenção Técnica (TRD M7)</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Inflow</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="20" t="n">
+      <c r="H8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="20" t="n">
+      <c r="I8" s="7" t="n">
         <v>83038.11</v>
       </c>
-      <c r="J8" s="27" t="n">
+      <c r="J8" s="25" t="n">
         <v>83038.11</v>
       </c>
     </row>
@@ -1515,479 +1584,497 @@
           <t>TOTAL DE ENTRADAS DE CAIXA (A)</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Total Inflows</t>
         </is>
       </c>
-      <c r="C9" s="31" t="n">
+      <c r="C9" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="31" t="n">
+      <c r="D9" s="28" t="n">
         <v>155269.92</v>
       </c>
-      <c r="E9" s="31" t="n">
+      <c r="E9" s="28" t="n">
         <v>264001.06</v>
       </c>
-      <c r="F9" s="31" t="n">
-        <v>348054.46</v>
-      </c>
-      <c r="G9" s="31" t="n">
-        <v>233397.32</v>
-      </c>
-      <c r="H9" s="31" t="n">
-        <v>304396.06</v>
-      </c>
-      <c r="I9" s="31" t="n">
+      <c r="F9" s="28" t="n">
+        <v>329961.79</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>239197.61</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>316688.44</v>
+      </c>
+      <c r="I9" s="28" t="n">
         <v>355643.46</v>
       </c>
-      <c r="J9" s="31" t="n">
+      <c r="J9" s="28" t="n">
         <v>1660762.28</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>2. SAÍDAS DE CAIXA (DESEMBOLSOS DE PRODUÇÃO E GESTÃO)</t>
         </is>
       </c>
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="24" t="n"/>
+      <c r="F10" s="24" t="n"/>
+      <c r="G10" s="24" t="n"/>
+      <c r="H10" s="24" t="n"/>
+      <c r="I10" s="24" t="n"/>
+      <c r="J10" s="24" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2.1 Equipe Técnica de Gestão (Engenheiro Residente + Mestre + TST)</t>
-        </is>
-      </c>
-      <c r="B11" s="28" t="inlineStr">
+          <t>2.1 Equipe Técnica de Gestão (Eng/Mestre/TST)</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>MO Gestão</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="5" t="n">
         <v>29300</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="5" t="n">
         <v>29300</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="5" t="n">
         <v>29300</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="5" t="n">
         <v>29300</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="5" t="n">
         <v>29300</v>
       </c>
-      <c r="H11" s="17" t="n">
+      <c r="H11" s="5" t="n">
         <v>29300</v>
       </c>
-      <c r="I11" s="17" t="n">
+      <c r="I11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="29" t="n">
+      <c r="J11" s="26" t="n">
         <v>175800</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>2.2 Vivência, Alimentação (16 op.) e Logística de Transporte</t>
-        </is>
-      </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>Vivência/Benefícios</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="n">
+          <t>2.2 Vivência, Alimentação (16 op.) e Transporte</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Vivência</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
         <v>23009.33</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="7" t="n">
         <v>23009.33</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="7" t="n">
         <v>23009.33</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="7" t="n">
         <v>23009.33</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="7" t="n">
         <v>23009.33</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="H12" s="7" t="n">
         <v>23009.33</v>
       </c>
-      <c r="I12" s="20" t="n">
+      <c r="I12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="27" t="n">
+      <c r="J12" s="25" t="n">
         <v>138055.98</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2.3 Mão de Obra Direta de Campo (Serviços Físicos Civis/Instalações)</t>
-        </is>
-      </c>
-      <c r="B13" s="28" t="inlineStr">
+          <t>2.3 Mão de Obra de Campo (Serviços Físicos)</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>MO Campo</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="5" t="n">
         <v>23588.7</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="5" t="n">
         <v>55068.46</v>
       </c>
-      <c r="E13" s="17" t="n">
-        <v>79403.53999999999</v>
-      </c>
-      <c r="F13" s="17" t="n">
-        <v>46208.08</v>
-      </c>
-      <c r="G13" s="17" t="n">
-        <v>67467.21000000001</v>
-      </c>
-      <c r="H13" s="17" t="n">
-        <v>60171.36</v>
-      </c>
-      <c r="I13" s="17" t="n">
+      <c r="E13" s="5" t="n">
+        <v>74165.36</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>47887.38</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>71026.09</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>60171.35</v>
+      </c>
+      <c r="I13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="29" t="n">
-        <v>331907.35</v>
+      <c r="J13" s="26" t="n">
+        <v>331907.34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>2.4 Materiais e Insumos Civis (Sinal / Entrada à Vista no Pedido)</t>
-        </is>
-      </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>Material D0</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="n">
+          <t>2.4 Materiais e Insumos Civis (Sinal à Vista)</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
         <v>8761.52</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="7" t="n">
         <v>20454</v>
       </c>
-      <c r="E14" s="20" t="n">
-        <v>29492.74</v>
-      </c>
-      <c r="F14" s="20" t="n">
-        <v>17163</v>
-      </c>
-      <c r="G14" s="20" t="n">
-        <v>25059.25</v>
-      </c>
-      <c r="H14" s="20" t="n">
+      <c r="E14" s="7" t="n">
+        <v>27547.13</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>17786.74</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>26381.12</v>
+      </c>
+      <c r="H14" s="7" t="n">
         <v>22349.36</v>
       </c>
-      <c r="I14" s="20" t="n">
+      <c r="I14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="27" t="n">
+      <c r="J14" s="25" t="n">
         <v>123279.87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2.5 Materiais e Insumos Civis (Faturamento a Prazo D+30)</t>
-        </is>
-      </c>
-      <c r="B15" s="28" t="inlineStr">
-        <is>
-          <t>Material D+30</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="n">
+          <t>2.5 Materiais e Insumos Civis (Prazo D+30)</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="5" t="n">
         <v>35046.07</v>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="5" t="n">
         <v>81815.99000000001</v>
       </c>
-      <c r="F15" s="17" t="n">
-        <v>117970.97</v>
-      </c>
-      <c r="G15" s="17" t="n">
-        <v>68652.02</v>
-      </c>
-      <c r="H15" s="17" t="n">
-        <v>100237</v>
-      </c>
-      <c r="I15" s="17" t="n">
+      <c r="F15" s="5" t="n">
+        <v>110188.54</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>71146.97</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>105524.48</v>
+      </c>
+      <c r="I15" s="5" t="n">
         <v>89397.44</v>
       </c>
-      <c r="J15" s="29" t="n">
+      <c r="J15" s="26" t="n">
         <v>493119.49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2.6 Locação de Containers NR-18 e Sanitários Químicos</t>
-        </is>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
+          <t>2.6 Locação de Containers NR-18 e Sanitários</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Equipamento</t>
         </is>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="7" t="n">
         <v>3191.66</v>
       </c>
-      <c r="D16" s="20" t="n">
+      <c r="D16" s="7" t="n">
         <v>6383.32</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="7" t="n">
         <v>6383.32</v>
       </c>
-      <c r="F16" s="20" t="n">
+      <c r="F16" s="7" t="n">
         <v>6383.32</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" s="7" t="n">
         <v>6383.32</v>
       </c>
-      <c r="H16" s="20" t="n">
+      <c r="H16" s="7" t="n">
         <v>6383.32</v>
       </c>
-      <c r="I16" s="20" t="n">
+      <c r="I16" s="7" t="n">
         <v>3191.66</v>
       </c>
-      <c r="J16" s="27" t="n">
+      <c r="J16" s="25" t="n">
         <v>38299.92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2.7 Contas de Consumo Provisórias (Energia, Água Pipa, Internet Fibra)</t>
-        </is>
-      </c>
-      <c r="B17" s="28" t="inlineStr">
+          <t>2.7 Contas de Consumo (Água, Luz, Internet)</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Canteiro</t>
         </is>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="5" t="n">
         <v>1175</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="5" t="n">
         <v>2350</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="5" t="n">
         <v>2350</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="5" t="n">
         <v>2350</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="5" t="n">
         <v>2350</v>
       </c>
-      <c r="H17" s="17" t="n">
+      <c r="H17" s="5" t="n">
         <v>2350</v>
       </c>
-      <c r="I17" s="17" t="n">
+      <c r="I17" s="5" t="n">
         <v>1175</v>
       </c>
-      <c r="J17" s="29" t="n">
+      <c r="J17" s="26" t="n">
         <v>14100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2.8 Tributos sobre Faturamento (ISS, PIS, COFINS, CPRB - 8,65% NF)</t>
-        </is>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
+          <t>2.8 Tributos sobre Faturamento (8,65% NF)</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Tributos</t>
         </is>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="C18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="20" t="n">
+      <c r="D18" s="7" t="n">
         <v>14137.73</v>
       </c>
-      <c r="E18" s="20" t="n">
+      <c r="E18" s="7" t="n">
         <v>24037.99</v>
       </c>
-      <c r="F18" s="20" t="n">
-        <v>31691.27</v>
-      </c>
-      <c r="G18" s="20" t="n">
-        <v>21251.44</v>
-      </c>
-      <c r="H18" s="20" t="n">
-        <v>27716.06</v>
-      </c>
-      <c r="I18" s="20" t="n">
+      <c r="F18" s="7" t="n">
+        <v>30043.89</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>21779.57</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>28835.32</v>
+      </c>
+      <c r="I18" s="7" t="n">
         <v>24821.43</v>
       </c>
-      <c r="J18" s="27" t="n">
-        <v>143655.92</v>
+      <c r="J18" s="25" t="n">
+        <v>143655.93</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2.9 Custos Indiretos Centrais BDI (Administração Central, Seguros e DF)</t>
-        </is>
-      </c>
-      <c r="B19" s="28" t="inlineStr">
-        <is>
-          <t>Indireto BDI</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="n">
+          <t>2.9 Custos Indiretos Centrais BDI (AC/Seguros)</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Indireto</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
         <v>16441.55</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="5" t="n">
         <v>16441.55</v>
       </c>
-      <c r="E19" s="17" t="n">
+      <c r="E19" s="5" t="n">
         <v>16441.55</v>
       </c>
-      <c r="F19" s="17" t="n">
+      <c r="F19" s="5" t="n">
         <v>16441.55</v>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="G19" s="5" t="n">
         <v>16441.55</v>
       </c>
-      <c r="H19" s="17" t="n">
+      <c r="H19" s="5" t="n">
         <v>16441.55</v>
       </c>
-      <c r="I19" s="17" t="n">
+      <c r="I19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="29" t="n">
+      <c r="J19" s="26" t="n">
         <v>98649.3</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>TOTAL DE SAÍDAS DE CAIXA (B)</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Total Outflows</t>
         </is>
       </c>
-      <c r="C20" s="27" t="n">
+      <c r="C20" s="25" t="n">
         <v>105467.76</v>
       </c>
-      <c r="D20" s="27" t="n">
+      <c r="D20" s="25" t="n">
         <v>202190.46</v>
       </c>
-      <c r="E20" s="27" t="n">
-        <v>292234.46</v>
-      </c>
-      <c r="F20" s="27" t="n">
-        <v>290517.52</v>
-      </c>
-      <c r="G20" s="27" t="n">
-        <v>259914.12</v>
-      </c>
-      <c r="H20" s="27" t="n">
-        <v>287957.98</v>
-      </c>
-      <c r="I20" s="27" t="n">
+      <c r="E20" s="25" t="n">
+        <v>285050.67</v>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>283390.75</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>267817.95</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>294364.71</v>
+      </c>
+      <c r="I20" s="25" t="n">
         <v>118585.53</v>
       </c>
-      <c r="J20" s="27" t="n">
+      <c r="J20" s="25" t="n">
         <v>1556867.83</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>3. RESULTADO OPERACIONAL E SALDOS DE CAIXA</t>
         </is>
       </c>
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="24" t="n"/>
+      <c r="G21" s="24" t="n"/>
+      <c r="H21" s="24" t="n"/>
+      <c r="I21" s="24" t="n"/>
+      <c r="J21" s="24" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>3.1 Saldo Operacional Líquido do Período (A - B)</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Resultado Líquido</t>
         </is>
       </c>
-      <c r="C22" s="27" t="n">
+      <c r="C22" s="25" t="n">
         <v>-105467.76</v>
       </c>
-      <c r="D22" s="27" t="n">
+      <c r="D22" s="25" t="n">
         <v>-46920.54</v>
       </c>
-      <c r="E22" s="27" t="n">
-        <v>-28233.4</v>
-      </c>
-      <c r="F22" s="27" t="n">
-        <v>57536.94</v>
-      </c>
-      <c r="G22" s="27" t="n">
-        <v>-26516.8</v>
-      </c>
-      <c r="H22" s="27" t="n">
-        <v>16438.08</v>
-      </c>
-      <c r="I22" s="27" t="n">
+      <c r="E22" s="25" t="n">
+        <v>-21049.61</v>
+      </c>
+      <c r="F22" s="25" t="n">
+        <v>46571.04</v>
+      </c>
+      <c r="G22" s="25" t="n">
+        <v>-28620.34</v>
+      </c>
+      <c r="H22" s="25" t="n">
+        <v>22323.73</v>
+      </c>
+      <c r="I22" s="25" t="n">
         <v>237057.93</v>
       </c>
-      <c r="J22" s="27" t="n">
+      <c r="J22" s="25" t="n">
         <v>103894.45</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="33" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>3.2 Saldo de Caixa Acumulado (Cenário Realista)</t>
         </is>
       </c>
-      <c r="B23" s="34" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>Acumulado</t>
         </is>
       </c>
-      <c r="C23" s="35" t="n">
+      <c r="C23" s="33" t="n">
         <v>-105467.76</v>
       </c>
-      <c r="D23" s="35" t="n">
+      <c r="D23" s="33" t="n">
         <v>-152388.3</v>
       </c>
-      <c r="E23" s="35" t="n">
-        <v>-180621.7</v>
-      </c>
-      <c r="F23" s="35" t="n">
-        <v>-123084.76</v>
-      </c>
-      <c r="G23" s="35" t="n">
-        <v>-149601.56</v>
-      </c>
-      <c r="H23" s="35" t="n">
+      <c r="E23" s="33" t="n">
+        <v>-173437.91</v>
+      </c>
+      <c r="F23" s="33" t="n">
+        <v>-126866.87</v>
+      </c>
+      <c r="G23" s="33" t="n">
+        <v>-155487.21</v>
+      </c>
+      <c r="H23" s="33" t="n">
         <v>-133163.48</v>
       </c>
-      <c r="I23" s="36" t="n">
+      <c r="I23" s="34" t="n">
         <v>103894.45</v>
       </c>
-      <c r="J23" s="37" t="n">
+      <c r="J23" s="35" t="n">
         <v>103894.45</v>
       </c>
     </row>
@@ -2033,69 +2120,69 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Cenário de Análise</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Premissas Chave de Fluxo</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="G2" s="15" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="H2" s="15" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>M6</t>
         </is>
       </c>
-      <c r="I2" s="15" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>M7</t>
         </is>
       </c>
-      <c r="J2" s="15" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>M8</t>
         </is>
       </c>
-      <c r="K2" s="15" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>Pico Negativo (R$)</t>
         </is>
       </c>
-      <c r="L2" s="15" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Saldo Final (R$)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="38" t="inlineStr">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>Cenário 1: Realista (Base)</t>
         </is>
@@ -2112,34 +2199,34 @@
         <v>-152388.3</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>-180621.7</v>
+        <v>-173437.91</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>-123084.76</v>
+        <v>-126866.87</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>-149601.56</v>
+        <v>-155487.21</v>
       </c>
       <c r="H3" s="18" t="n">
         <v>-133163.48</v>
       </c>
-      <c r="I3" s="22" t="n">
+      <c r="I3" s="21" t="n">
         <v>103894.45</v>
       </c>
-      <c r="J3" s="39" t="inlineStr">
+      <c r="J3" s="37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="K3" s="18" t="n">
-        <v>-180621.7</v>
-      </c>
-      <c r="L3" s="29" t="n">
+        <v>-173437.91</v>
+      </c>
+      <c r="L3" s="26" t="n">
         <v>103894.45</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>Cenário 2: Otimista (Adiantamento)</t>
         </is>
@@ -2149,41 +2236,41 @@
           <t>Adiantamento Contratual de 10% amortizado em 4x nas medições</t>
         </is>
       </c>
-      <c r="C4" s="40" t="n">
+      <c r="C4" s="38" t="n">
         <v>60608.47</v>
       </c>
-      <c r="D4" s="21" t="n">
+      <c r="D4" s="20" t="n">
         <v>-27831.13</v>
       </c>
-      <c r="E4" s="21" t="n">
-        <v>-97583.59</v>
-      </c>
-      <c r="F4" s="21" t="n">
-        <v>-81565.71000000001</v>
-      </c>
-      <c r="G4" s="21" t="n">
-        <v>-149601.57</v>
-      </c>
-      <c r="H4" s="21" t="n">
+      <c r="E4" s="20" t="n">
+        <v>-90399.8</v>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>-85347.82000000001</v>
+      </c>
+      <c r="G4" s="20" t="n">
+        <v>-155487.22</v>
+      </c>
+      <c r="H4" s="20" t="n">
         <v>-133163.49</v>
       </c>
-      <c r="I4" s="40" t="n">
+      <c r="I4" s="38" t="n">
         <v>103894.44</v>
       </c>
-      <c r="J4" s="41" t="inlineStr">
+      <c r="J4" s="39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K4" s="21" t="n">
-        <v>-149601.57</v>
-      </c>
-      <c r="L4" s="27" t="n">
+      <c r="K4" s="20" t="n">
+        <v>-155487.22</v>
+      </c>
+      <c r="L4" s="25" t="n">
         <v>103894.44</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Cenário 3: Estresse (Atraso 30d)</t>
         </is>
@@ -2200,27 +2287,27 @@
         <v>-307658.22</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>-444622.76</v>
+        <v>-437438.97</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>-471139.22</v>
+        <v>-456828.66</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>-382998.88</v>
+        <v>-394684.82</v>
       </c>
       <c r="H5" s="18" t="n">
-        <v>-437559.54</v>
+        <v>-449851.92</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>-251749.01</v>
       </c>
-      <c r="J5" s="22" t="n">
+      <c r="J5" s="21" t="n">
         <v>103894.45</v>
       </c>
       <c r="K5" s="18" t="n">
-        <v>-471139.22</v>
-      </c>
-      <c r="L5" s="29" t="n">
+        <v>-456828.66</v>
+      </c>
+      <c r="L5" s="26" t="n">
         <v>103894.45</v>
       </c>
     </row>
